--- a/Cote기록.xlsx
+++ b/Cote기록.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Heetae\source\repos\Cote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3223FB-1538-4E8B-914B-AED42D422238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9570FA-051F-41D8-B182-8D65996E41C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D201B5D2-2DDF-4A7B-B11F-7425E7B6E507}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="184">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -870,6 +870,131 @@
   </si>
   <si>
     <t>숫자 게임</t>
+  </si>
+  <si>
+    <t>보석 쇼핑</t>
+  </si>
+  <si>
+    <t>파괴되지 않은 건물</t>
+  </si>
+  <si>
+    <t>이모스법</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">전형적인 이모스법 문제. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다시 풀어보자</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로또의 최고 순위와 최저 순위</t>
+  </si>
+  <si>
+    <t>봉인된 주문</t>
+  </si>
+  <si>
+    <t>엑셀컬럼넘버링</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0이 없는 26진수와 유사한 개념의 엑셀 컬럼 &lt;-&gt; 넘버링 변환 문제</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[PCCP 기출문제] 4번 / 수식 복원하기</t>
+  </si>
+  <si>
+    <t>요격 시스템</t>
+  </si>
+  <si>
+    <t>연속된 부분 수열의 합</t>
+  </si>
+  <si>
+    <t>그리디-투포인터</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제 진행하기</t>
+  </si>
+  <si>
+    <t>광물 캐기</t>
+  </si>
+  <si>
+    <t>리코쳇 로봇</t>
+  </si>
+  <si>
+    <t>당구 연습</t>
+  </si>
+  <si>
+    <t>혼자서 하는 틱택토</t>
+  </si>
+  <si>
+    <t>3X3 오목에서는 DP는 필요없지만, NxN 일 경우 DP가 반드시 필요. 그런데 DP로직으로 하면 97.5로 하나를 놓침.. 원인 못찾음</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>호텔 대실</t>
+  </si>
+  <si>
+    <t>이모스</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>무인도 여행</t>
+  </si>
+  <si>
+    <t>뒤에 있는 큰 수 찾기</t>
+  </si>
+  <si>
+    <t>단조스택</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자 변환하기</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">전형적 DP인데 이걸 캐치못했네.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다시 풀어보자</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이모티콘 할인행사</t>
+  </si>
+  <si>
+    <t>마법의 엘리베이터</t>
+  </si>
+  <si>
+    <t>DP로 풀으면 53만 나옴..</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>디펜스 게임</t>
+  </si>
+  <si>
+    <t>PriorityQueue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1002,7 +1127,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1061,6 +1186,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1378,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3558EF3-1756-4B11-A588-6324C788ED8F}">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -3448,6 +3576,449 @@
       </c>
       <c r="H87" s="8" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B88" s="8">
+        <v>3</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="F88" s="12">
+        <v>110</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A89" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B89" s="8">
+        <v>3</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="F89" s="12">
+        <v>40</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I89" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A90" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B90" s="8">
+        <v>1</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B91" s="8">
+        <v>3</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F91" s="12">
+        <v>100</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I91" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A92" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B92" s="8">
+        <v>3</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F92" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A93" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B93" s="8">
+        <v>2</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="E93" s="2">
+        <v>1</v>
+      </c>
+      <c r="F93" s="12">
+        <v>34</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A94" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B94" s="8">
+        <v>2</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E94" s="2">
+        <v>1</v>
+      </c>
+      <c r="F94" s="12">
+        <v>16</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I94" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A95" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B95" s="8">
+        <v>2</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="E95" s="2">
+        <v>1</v>
+      </c>
+      <c r="F95" s="12">
+        <v>33</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A96" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B96" s="8">
+        <v>2</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F96" s="12">
+        <v>49</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A97" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B97" s="8">
+        <v>2</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="E97" s="2">
+        <v>1</v>
+      </c>
+      <c r="F97" s="12">
+        <v>41</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A98" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B98" s="8">
+        <v>2</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="E98" s="2">
+        <v>1</v>
+      </c>
+      <c r="F98" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A99" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B99" s="8">
+        <v>2</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="F99" s="12">
+        <v>40</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I99" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A100" s="1">
+        <v>45978</v>
+      </c>
+      <c r="B100" s="8">
+        <v>2</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="E100" s="2">
+        <v>1</v>
+      </c>
+      <c r="F100" s="12">
+        <v>20</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A101" s="1">
+        <v>45978</v>
+      </c>
+      <c r="B101" s="8">
+        <v>2</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="E101" s="2">
+        <v>1</v>
+      </c>
+      <c r="F101" s="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A102" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B102" s="8">
+        <v>2</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="F102" s="12">
+        <v>10</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I102" s="20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A103" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B103" s="8">
+        <v>2</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F103" s="12">
+        <v>20</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I103" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A104" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B104" s="8">
+        <v>2</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="E104" s="2">
+        <v>1</v>
+      </c>
+      <c r="F104" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A105" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B105" s="8">
+        <v>2</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="F105" s="12">
+        <v>28</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I105" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A106" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B106" s="8">
+        <v>2</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F106" s="12">
+        <v>20</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3539,8 +4110,27 @@
     <hyperlink ref="C85" r:id="rId84" display="https://school.programmers.co.kr/learn/courses/30/lessons/118668" xr:uid="{118B748E-890A-48C8-BD35-96E1E40C394C}"/>
     <hyperlink ref="C86" r:id="rId85" display="https://school.programmers.co.kr/learn/courses/30/lessons/118667" xr:uid="{BF3F2388-23E2-4345-8C54-48049FA987E6}"/>
     <hyperlink ref="C87" r:id="rId86" display="https://school.programmers.co.kr/learn/courses/30/lessons/12987" xr:uid="{20763C57-D061-4088-AAC7-7895822C921B}"/>
+    <hyperlink ref="C88" r:id="rId87" display="https://school.programmers.co.kr/learn/courses/30/lessons/67258" xr:uid="{C1DCD0F0-374C-4C11-B09F-961BC5E0CE00}"/>
+    <hyperlink ref="C89" r:id="rId88" display="https://school.programmers.co.kr/learn/courses/30/lessons/92344" xr:uid="{0236FADC-D9B5-4AA0-B118-FDF166F2811D}"/>
+    <hyperlink ref="C90" r:id="rId89" display="https://school.programmers.co.kr/learn/courses/30/lessons/77484" xr:uid="{40ADAA9D-AA19-4B33-BEFB-FDB3517ED730}"/>
+    <hyperlink ref="C91" r:id="rId90" display="https://school.programmers.co.kr/learn/courses/30/lessons/389481" xr:uid="{4A5B9835-F38A-4753-9562-C9FBCE6D114C}"/>
+    <hyperlink ref="C92" r:id="rId91" display="https://school.programmers.co.kr/learn/courses/30/lessons/340210" xr:uid="{2B9281DD-4684-4ED6-B945-DC4F7537C79C}"/>
+    <hyperlink ref="C93" r:id="rId92" display="https://school.programmers.co.kr/learn/courses/30/lessons/181188" xr:uid="{CBAD7D92-37F1-41BB-ACB7-5CC53636FB88}"/>
+    <hyperlink ref="C94" r:id="rId93" display="https://school.programmers.co.kr/learn/courses/30/lessons/178870" xr:uid="{ED9DA887-11E9-4189-942B-628CC0C7DB30}"/>
+    <hyperlink ref="C95" r:id="rId94" display="https://school.programmers.co.kr/learn/courses/30/lessons/176962" xr:uid="{20C7CF90-4C72-43D3-B27B-53A55C361A97}"/>
+    <hyperlink ref="C96" r:id="rId95" display="https://school.programmers.co.kr/learn/courses/30/lessons/172927" xr:uid="{4B7FFC15-07C8-4F22-85FB-3491BF61D89E}"/>
+    <hyperlink ref="C97" r:id="rId96" display="https://school.programmers.co.kr/learn/courses/30/lessons/169199" xr:uid="{9AA8B453-2EB5-4412-B120-0F85F6C932BC}"/>
+    <hyperlink ref="C98" r:id="rId97" display="https://school.programmers.co.kr/learn/courses/30/lessons/169198" xr:uid="{B430E4F9-5EE8-4A62-AB9B-12392A0B082B}"/>
+    <hyperlink ref="C99" r:id="rId98" display="https://school.programmers.co.kr/learn/courses/30/lessons/160585" xr:uid="{26C197C9-7F91-414F-94B6-E99FA3AF1878}"/>
+    <hyperlink ref="C100" r:id="rId99" display="https://school.programmers.co.kr/learn/courses/30/lessons/155651" xr:uid="{FEC4D9F5-DEB8-47E9-B5EB-5FE8B6A0BC8A}"/>
+    <hyperlink ref="C101" r:id="rId100" display="https://school.programmers.co.kr/learn/courses/30/lessons/154540" xr:uid="{5FB5B5C0-DFD6-4ECD-9942-36BB5350D058}"/>
+    <hyperlink ref="C102" r:id="rId101" display="https://school.programmers.co.kr/learn/courses/30/lessons/154539" xr:uid="{277A5A5B-2E20-4112-9E04-3B1CAAD0B3A1}"/>
+    <hyperlink ref="C103" r:id="rId102" display="https://school.programmers.co.kr/learn/courses/30/lessons/154538" xr:uid="{5CCE58C3-EDC6-41BF-A630-1F6BC9BDA134}"/>
+    <hyperlink ref="C104" r:id="rId103" display="https://school.programmers.co.kr/learn/courses/30/lessons/150368" xr:uid="{D66D1B29-A3CA-47DA-9FF6-AC0E2FF22494}"/>
+    <hyperlink ref="C105" r:id="rId104" display="https://school.programmers.co.kr/learn/courses/30/lessons/148653" xr:uid="{6346A0F7-D4C0-4B33-85E9-DBD92B179A99}"/>
+    <hyperlink ref="C106" r:id="rId105" display="https://school.programmers.co.kr/learn/courses/30/lessons/142085" xr:uid="{0318BFD8-3BAE-4C17-815A-CE2B0AEED7F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId87"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId106"/>
 </worksheet>
 </file>